--- a/scripts/productos-digitales/guia-chocolateria/build/campanas-y-valle-del-ano.xlsx
+++ b/scripts/productos-digitales/guia-chocolateria/build/campanas-y-valle-del-ano.xlsx
@@ -283,7 +283,7 @@
   <commentList>
     <comment ref="B16" authorId="0" shapeId="0">
       <text>
-        <t>Verificado el 12-09-2026 · Ley 37/1992, de 28 de diciembre, del Impuesto sobre el Valor Añadido (BOE-A-1992-28740), texto consolidado · «Última modificación: 28 de febrero de 2026» (Art. 91.Dos.1.1.º (las siete letras: pan común, harinas panificables, leches, quesos, huevos, frutas/verduras/hortalizas/legumbres/tubérc...) · https://www.boe.es/buscar/act.php?id=BOE-A-1992-28740</t>
+        <t>Verificado el 12-09-2026 · Ley 37/1992, de 28 de diciembre, del Impuesto sobre el Valor Añadido (BOE-A-1992-28740), texto consolidado · «Última modificación: 28 de febrero de 2026» (Art. 91.Dos.1.1.º (las siete letras: pan común, harinas panificables, leches, qu...) · https://www.boe.es/buscar/act.php?id=BOE-A-1992-28740</t>
       </text>
     </comment>
     <comment ref="B19" authorId="0" shapeId="0">
@@ -2629,7 +2629,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Peso Sobre el Año</t>
+          <t>Peso sobre el Año</t>
         </is>
       </c>
     </row>
